--- a/Recursos/Importar/plantilla_listadoConvenios.xlsx
+++ b/Recursos/Importar/plantilla_listadoConvenios.xlsx
@@ -2,63 +2,96 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\PROYECTO\Recursos\Importar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pruebas\Recursos\Importar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F7F093-3EE9-44B9-B3FA-488E91AA2FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3DF7E9-000F-430C-B2EF-CE557FEF2D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Convenios" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Nº Convenio</t>
-  </si>
-  <si>
-    <t>Nombre de la Empresa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Nº CONV.</t>
+  </si>
+  <si>
+    <t>NOMBRE DE EMPRESA</t>
   </si>
   <si>
     <t>CIF</t>
   </si>
   <si>
-    <t>Dirección</t>
-  </si>
-  <si>
-    <t>Municipio</t>
+    <t>DIRECCION</t>
+  </si>
+  <si>
+    <t>LOCALIDAD</t>
   </si>
   <si>
     <t>CP</t>
   </si>
   <si>
-    <t>País</t>
-  </si>
-  <si>
-    <t>Teléfono</t>
-  </si>
-  <si>
-    <t>Fax</t>
-  </si>
-  <si>
-    <t>Mail</t>
-  </si>
-  <si>
-    <t>Nombre Representante</t>
-  </si>
-  <si>
-    <t>DNI Representante</t>
-  </si>
-  <si>
-    <t>Cargo</t>
+    <t>TELEFONO</t>
+  </si>
+  <si>
+    <t>FAX</t>
+  </si>
+  <si>
+    <t>REPRESENTANTE</t>
+  </si>
+  <si>
+    <t>ESPECIALIDAD</t>
+  </si>
+  <si>
+    <t>FECHA DE ALTA O RENOVACION CONV</t>
+  </si>
+  <si>
+    <t>FECHA NUEVA RENOVACIÓN</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>A001</t>
+  </si>
+  <si>
+    <t>EMPRESA EJEMPLO S.L.</t>
+  </si>
+  <si>
+    <t>B12345678</t>
+  </si>
+  <si>
+    <t>Calle Mayor, 1</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>28001</t>
+  </si>
+  <si>
+    <t>910000000</t>
+  </si>
+  <si>
+    <t>Juan Pérez López</t>
+  </si>
+  <si>
+    <t>DAW</t>
+  </si>
+  <si>
+    <t>01.01.25</t>
+  </si>
+  <si>
+    <t>01.01.27</t>
   </si>
 </sst>
 </file>
@@ -67,32 +100,40 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="10"/>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -100,21 +141,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -127,9 +186,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,44 +196,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -201,32 +260,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -253,27 +294,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -282,228 +305,267 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="2" width="24.09765625" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" customWidth="1"/>
-    <col min="4" max="4" width="16.09765625" customWidth="1"/>
-    <col min="5" max="5" width="15.09765625" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" customWidth="1"/>
-    <col min="7" max="7" width="9.3984375" customWidth="1"/>
-    <col min="8" max="8" width="13.69921875" customWidth="1"/>
-    <col min="9" max="9" width="11.296875" customWidth="1"/>
-    <col min="10" max="10" width="13.09765625" customWidth="1"/>
-    <col min="11" max="11" width="24.8984375" customWidth="1"/>
-    <col min="12" max="12" width="23.296875" customWidth="1"/>
-    <col min="13" max="13" width="12.19921875" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="1"/>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{843dcbeb-75d9-4d0b-88ed-da30b35a541e}" enabled="1" method="Privileged" siteId="{d1bbc304-0aa9-40a0-ad0f-d5f10a43e6a3}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/Recursos/Importar/plantilla_listadoConvenios.xlsx
+++ b/Recursos/Importar/plantilla_listadoConvenios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pruebas\Recursos\Importar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3DF7E9-000F-430C-B2EF-CE557FEF2D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F312FD6-65AA-4C8B-9073-9A19AFF0BFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Nº CONV.</t>
   </si>
@@ -79,19 +79,16 @@
     <t>28001</t>
   </si>
   <si>
-    <t>910000000</t>
-  </si>
-  <si>
     <t>Juan Pérez López</t>
   </si>
   <si>
-    <t>DAW</t>
-  </si>
-  <si>
     <t>01.01.25</t>
   </si>
   <si>
     <t>01.01.27</t>
+  </si>
+  <si>
+    <t>DAW 2º</t>
   </si>
 </sst>
 </file>
@@ -107,20 +104,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF888888"/>
+      <b/>
+      <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <sz val="8"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,7 +125,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,33 +146,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -488,22 +509,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -512,13 +533,13 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -529,41 +550,41 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6">
+        <v>910000000</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
